--- a/output/pdf_financials_xlsx/FMS.xlsx
+++ b/output/pdf_financials_xlsx/FMS.xlsx
@@ -1243,10 +1243,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>7.799</v>
+        <v>-7.799</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>12.0292</v>
+        <v>-12.0292</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -41824,10 +41824,10 @@
         </is>
       </c>
       <c r="E361" s="5" t="n">
-        <v>0.15598</v>
+        <v>-0.15598</v>
       </c>
       <c r="F361" s="5" t="n">
-        <v>0.240584</v>
+        <v>-0.240584</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FMS.xlsx
+++ b/output/pdf_financials_xlsx/FMS.xlsx
@@ -1026,43 +1026,43 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.079083</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.249868</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.208278</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.074555</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.006109</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.008359</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.000366</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.00053</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.006585</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.008038</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.000197</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.000139</v>
       </c>
     </row>
     <row r="13">
@@ -2019,43 +2019,43 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.994792</v>
+        <v>-4.073875</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-10.321059</v>
+        <v>-10.570927</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-4.618788</v>
+        <v>-4.827066</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-6.050702</v>
+        <v>-6.125257</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.015333</v>
+        <v>-5.021442</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-3.662557</v>
+        <v>-3.670916</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-6.528031</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.152318</v>
+        <v>-2.152684</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-4.49684</v>
+        <v>-4.49737</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-4.805407</v>
+        <v>-4.811992</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.658483</v>
+        <v>-4.666521</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-1.975745</v>
+        <v>-1.975942</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-2.598663</v>
+        <v>-2.598802</v>
       </c>
     </row>
     <row r="28">
@@ -2133,43 +2133,43 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.994792</v>
+        <v>-4.073875</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-10.003861</v>
+        <v>-10.253729</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.040448</v>
+        <v>-4.248726</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.010383</v>
+        <v>-6.084938</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.015333</v>
+        <v>-5.021442</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.662557</v>
+        <v>-3.670916</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-6.528031</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.152318</v>
+        <v>-2.152684</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-4.49684</v>
+        <v>-4.49737</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.805407</v>
+        <v>-4.811992</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.658483</v>
+        <v>-4.666521</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.975745</v>
+        <v>-1.975942</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-2.598663</v>
+        <v>-2.598802</v>
       </c>
     </row>
     <row r="30">
@@ -2417,52 +2417,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001576</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.006594</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.612897</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>17.063652</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>17.669866</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>12.174671</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.200634</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.400443</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.085731</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.322665</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.110835</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.473783</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.137711</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.001688</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.575952</v>
       </c>
     </row>
     <row r="35">
@@ -2527,52 +2527,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001576</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.006594</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.300533</v>
+        <v>0.91343</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.91194</v>
+        <v>18.975592</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>2.112845</v>
+        <v>19.782711</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>12.174671</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.200634</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.400443</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.085731</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.322665</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.110835</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000109</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.473783</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.137711</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.001688</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.575952</v>
       </c>
     </row>
     <row r="37">
@@ -3187,49 +3187,49 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.009003000000000001</v>
+        <v>0.007427</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.010376</v>
+        <v>0.003782</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.664328</v>
+        <v>0.051431</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>18.078699</v>
+        <v>1.015047</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>18.65888</v>
+        <v>0.9890139999999999</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>13.910281</v>
+        <v>1.73561</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.537893</v>
+        <v>0.337259</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.249147</v>
+        <v>0.848704</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.746086</v>
+        <v>0.660355</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.62703</v>
+        <v>1.304365</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.923944</v>
+        <v>0.813109</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.752541</v>
+        <v>0.752432</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.615693</v>
+        <v>1.14191</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.122753</v>
+        <v>0.985042</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.058306</v>
+        <v>0.056618</v>
       </c>
       <c r="Q48" s="3" t="n">
         <v>0</v>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -30468,7 +30468,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -32440,7 +32440,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -34150,7 +34150,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">

--- a/output/pdf_financials_xlsx/FMS.xlsx
+++ b/output/pdf_financials_xlsx/FMS.xlsx
@@ -2082,19 +2082,19 @@
         <v>0.317198</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.57834</v>
+        <v>0.635883</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.040319</v>
+        <v>0.075792</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.033203</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.026922</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.014801</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>0</v>
@@ -2139,19 +2139,19 @@
         <v>-10.253729</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-4.248726</v>
+        <v>-4.191183</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-6.084938</v>
+        <v>-6.049465</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-5.021442</v>
+        <v>-4.988239</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.670916</v>
+        <v>-3.643994</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.528031</v>
+        <v>-6.51323</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-2.152684</v>
@@ -6109,22 +6109,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.317198</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.635883</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.075792</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.033203</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.026922</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.014801</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>0</v>
@@ -23136,7 +23136,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -24700,7 +24704,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -33680,7 +33684,11 @@
           <t>Depreciation of property and equipment (Note 7)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -36672,7 +36680,7 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
@@ -37534,7 +37542,11 @@
           <t>Depreciation of property and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -37630,7 +37642,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -40012,7 +40024,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -40864,7 +40876,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">

--- a/output/pdf_financials_xlsx/FMS.xlsx
+++ b/output/pdf_financials_xlsx/FMS.xlsx
@@ -6700,7 +6700,7 @@
         <v>0</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N110" s="3" t="n">
         <v>0</v>
@@ -6988,13 +6988,13 @@
         <v>0</v>
       </c>
       <c r="N115" s="3" t="n">
-        <v>0</v>
+        <v>0.131698</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>0.195899</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.185852</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -7021,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.060092</v>
       </c>
       <c r="H116" s="3" t="n">
         <v>0</v>
@@ -18716,7 +18716,11 @@
           <t>Proceeds from sale of marketable securities (Note 4)</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -21944,7 +21948,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -26716,7 +26724,11 @@
           <t>Acquisition of intangible assets</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
